--- a/01-foundations/patient-waiting-time-analysis.xlsx
+++ b/01-foundations/patient-waiting-time-analysis.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Predator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Predator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E308E4D-CB13-4665-BBBB-807186C515AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891FA8DA-D11F-4BF6-87FB-4FF5B312CD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="65">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -230,7 +231,10 @@
     <t>P050</t>
   </si>
   <si>
-    <t>Los datos muestran una tendencia negativa: los pacientes con menores tiempos de espera presentan niveles de satisfacción más altos, mientras que los pacientes con mayores tiempos de espera presentan menor satisfacción.</t>
+    <t>Tratamiento</t>
+  </si>
+  <si>
+    <t>Satisfacción promedio</t>
   </si>
 </sst>
 </file>
@@ -274,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -282,8 +286,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,7 +921,334 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Satisfacción promedio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$I$2:$I$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Sports</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Musculoskeletal</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Neurological</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Remedial Massage</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5833333333333335</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.7777777777777777</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1F86-4D1F-A145-985737BED930}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1120346752"/>
+        <c:axId val="1248388560"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1120346752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248388560"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1248388560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1120346752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1455,6 +1785,509 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1699,6 +2532,149 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A0BD98E-D30C-3559-13FE-C828A121DA17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4381500" cy="2159053"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0083FA4A-C09F-98E3-7172-8DE5F9873288}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7414260" y="4084320"/>
+          <a:ext cx="4381500" cy="2159053"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Pregunta:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>¿Qué tipo de tratamiento presenta el mayor nivel promedio de satisfacción?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Hallazgo:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>Remedial Massage presenta la mayor satisfacción promedio (4,78), seguido de Sports (4,5). Neurological presenta el promedio más bajo (2,58).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Conclusión:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>En estos datos, los tratamientos de Remedial Massage y Sports presentan mayores niveles de satisfacción promedio que Musculoskeletal y Neurological.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2516,7 +3492,6 @@
       <c r="G21" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -2587,7 +3562,6 @@
       <c r="G24" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -2634,7 +3608,1240 @@
       <c r="G26" t="s">
         <v>9</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="E27">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>36</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>19</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>15</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>26</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>21</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>34</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41">
+        <v>62</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>13</v>
+      </c>
+      <c r="E41">
+        <v>30</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>7</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>27</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45">
+        <v>69</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>39</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47">
+        <v>40</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48">
+        <v>53</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>16</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51">
+        <v>51</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>23</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98949D8-3C81-4718-B70E-75962FBE0715}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" customWidth="1"/>
+    <col min="10" max="10" width="36.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGEIF(C2:C51,I2,F2:F51)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J5" si="0">AVERAGEIF(C3:C52,I3,F3:F52)</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>2.5833333333333335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>4.7777777777777777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>35</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>18</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>32</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>38</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>27</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>24</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>33</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>16</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">

--- a/01-foundations/patient-waiting-time-analysis.xlsx
+++ b/01-foundations/patient-waiting-time-analysis.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Predator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891FA8DA-D11F-4BF6-87FB-4FF5B312CD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9F12D1-EB64-4012-A123-253D6BA1B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" r:id="rId1"/>
+    <sheet name="analisis proyecto 1" sheetId="2" r:id="rId2"/>
+    <sheet name="analisis proyecto 2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="63">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -230,12 +231,6 @@
   <si>
     <t>P050</t>
   </si>
-  <si>
-    <t>Tratamiento</t>
-  </si>
-  <si>
-    <t>Satisfacción promedio</t>
-  </si>
 </sst>
 </file>
 
@@ -385,7 +380,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$1</c:f>
+              <c:f>datos!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -418,7 +413,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$51</c:f>
+              <c:f>datos!$E$2:$E$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -577,7 +572,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$51</c:f>
+              <c:f>datos!$F$2:$F$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -936,6 +931,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Satisfaction_Score</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -977,11 +997,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$J$1</c:f>
+              <c:f>'analisis proyecto 1'!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Satisfacción promedio</c:v>
+                  <c:v>Satisfaction_Score</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -998,7 +1018,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet2!$I$2:$I$5</c:f>
+              <c:f>'analisis proyecto 1'!$I$2:$I$5</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1018,7 +1038,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$J$2:$J$5</c:f>
+              <c:f>'analisis proyecto 1'!$J$2:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1208,6 +1228,346 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Satisfaction_Score and sessions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'analisis proyecto 2'!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Satisfaction_Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'analisis proyecto 2'!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.8571428571428568</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8888888888888893</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'analisis proyecto 2'!$K$2:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5833333333333335</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.7777777777777777</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E38A-4F77-B226-3EA0BC34966A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1387523744"/>
+        <c:axId val="1388386864"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1387523744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1388386864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1388386864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1387523744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1288,6 +1648,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2288,6 +2688,522 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2355,8 +3271,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>5674659</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>170330</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2372,7 +3288,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6728013" y="3433482"/>
-          <a:ext cx="5499846" cy="1936377"/>
+          <a:ext cx="5499846" cy="2133600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2444,6 +3360,17 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX" sz="1100" b="1" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -2675,6 +3602,149 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4381500" cy="2503506"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3752A63-DF22-4A83-9496-50DCCE970257}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7414260" y="4084320"/>
+          <a:ext cx="4381500" cy="2503506"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Pregunta:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-MX"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>¿Qué relación existe entre el número promedio de sesiones y la satisfacción de los pacientes según el tipo de tratamiento?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Hallazgo:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-MX"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>Los tratamientos con menos sesiones promedio, como Sports y Remedial Massage, presentan mayores niveles de satisfacción. Neurological tiene el mayor número promedio de sesiones (12,5) y la menor satisfacción (2,58).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" b="1"/>
+            <a:t>Conclusión:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-MX"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-MX"/>
+            <a:t>En estos datos se observa una tendencia negativa: los tratamientos con mayor número promedio de sesiones presentan menores niveles de satisfacción.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>40341</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>143435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>856129</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>17930</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6313F5FE-D98E-58BE-D7B3-A713A9865698}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4231,10 +5301,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -4588,6 +5658,1259 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>38</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>27</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>24</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>33</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>16</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="E27">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>36</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>19</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>15</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>26</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>21</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>34</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41">
+        <v>62</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>13</v>
+      </c>
+      <c r="E41">
+        <v>30</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>7</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>27</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45">
+        <v>69</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>39</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47">
+        <v>40</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48">
+        <v>53</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>16</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51">
+        <v>51</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>23</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE73DF97-8264-48A8-B67E-7D26DCCE4328}">
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" customWidth="1"/>
+    <col min="10" max="10" width="36.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGEIF($C$2:$C$51,I2,$D$2:$D$51)</f>
+        <v>5.8571428571428568</v>
+      </c>
+      <c r="K2">
+        <f>AVERAGEIF($C$2:$C$51,I2,$F$2:$F$51)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J5" si="0">AVERAGEIF($C$2:$C$51,I3,$D$2:$D$51)</f>
+        <v>7.7333333333333334</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K5" si="1">AVERAGEIF($C$2:$C$51,I3,$F$2:$F$51)</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>2.5833333333333335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5.8888888888888893</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>4.7777777777777777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>35</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>18</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>32</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>

--- a/01-foundations/patient-waiting-time-analysis.xlsx
+++ b/01-foundations/patient-waiting-time-analysis.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Predator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9F12D1-EB64-4012-A123-253D6BA1B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5EC521-61D0-4410-893C-F5EBA6824C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8EFE0B5-3DBC-4934-B737-96350E6A8220}"/>
   </bookViews>
   <sheets>
-    <sheet name="datos" sheetId="1" r:id="rId1"/>
-    <sheet name="analisis proyecto 1" sheetId="2" r:id="rId2"/>
-    <sheet name="analisis proyecto 2" sheetId="4" r:id="rId3"/>
+    <sheet name="analisis proyecto 1 " sheetId="1" r:id="rId1"/>
+    <sheet name="analisis proyecto 2 " sheetId="2" r:id="rId2"/>
+    <sheet name="analisis proyecto 3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -380,7 +380,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>datos!$F$1</c:f>
+              <c:f>'analisis proyecto 1 '!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -413,7 +413,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>datos!$E$2:$E$51</c:f>
+              <c:f>'analisis proyecto 1 '!$E$2:$E$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -572,7 +572,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>datos!$F$2:$F$51</c:f>
+              <c:f>'analisis proyecto 1 '!$F$2:$F$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -997,7 +997,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'analisis proyecto 1'!$J$1</c:f>
+              <c:f>'analisis proyecto 2 '!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1018,7 +1018,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'analisis proyecto 1'!$I$2:$I$5</c:f>
+              <c:f>'analisis proyecto 2 '!$I$2:$I$5</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1038,7 +1038,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'analisis proyecto 1'!$J$2:$J$5</c:f>
+              <c:f>'analisis proyecto 2 '!$J$2:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1308,7 +1308,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'analisis proyecto 2'!$K$1</c:f>
+              <c:f>'analisis proyecto 3'!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1341,7 +1341,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'analisis proyecto 2'!$J$2:$J$5</c:f>
+              <c:f>'analisis proyecto 3'!$J$2:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1362,7 +1362,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'analisis proyecto 2'!$K$2:$K$5</c:f>
+              <c:f>'analisis proyecto 3'!$K$2:$K$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
